--- a/data/crime-stats.xlsx
+++ b/data/crime-stats.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -843,41 +843,41 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>28110</v>
+        <v>28125</v>
       </c>
       <c r="B27" t="str">
-        <v>중구</v>
+        <v>제물포구</v>
       </c>
       <c r="C27">
-        <v>378</v>
+        <v>310</v>
       </c>
       <c r="D27">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="E27">
-        <v>1510</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>28140</v>
+        <v>28155</v>
       </c>
       <c r="B28" t="str">
-        <v>동구</v>
+        <v>영종구</v>
       </c>
       <c r="C28">
-        <v>253</v>
+        <v>320</v>
       </c>
       <c r="D28">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="E28">
-        <v>1580</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>28170</v>
+        <v>28177</v>
       </c>
       <c r="B29" t="str">
         <v>미추홀구</v>
@@ -962,16 +962,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>28260</v>
+        <v>28275</v>
       </c>
       <c r="B34" t="str">
-        <v>서구</v>
+        <v>서해구</v>
       </c>
       <c r="C34">
-        <v>2136</v>
+        <v>1382</v>
       </c>
       <c r="D34">
-        <v>270000</v>
+        <v>175000</v>
       </c>
       <c r="E34">
         <v>790</v>
@@ -979,339 +979,339 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>28710</v>
+        <v>28290</v>
       </c>
       <c r="B35" t="str">
-        <v>강화군</v>
+        <v>검단구</v>
       </c>
       <c r="C35">
-        <v>268</v>
+        <v>750</v>
       </c>
       <c r="D35">
-        <v>69000</v>
+        <v>95000</v>
       </c>
       <c r="E35">
-        <v>390</v>
+        <v>790</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>28720</v>
+        <v>28710</v>
       </c>
       <c r="B36" t="str">
-        <v>옹진군</v>
+        <v>강화군</v>
       </c>
       <c r="C36">
-        <v>56</v>
+        <v>268</v>
       </c>
       <c r="D36">
-        <v>20000</v>
+        <v>69000</v>
       </c>
       <c r="E36">
-        <v>280</v>
+        <v>390</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>41110</v>
+        <v>28720</v>
       </c>
       <c r="B37" t="str">
-        <v>수원시</v>
+        <v>옹진군</v>
       </c>
       <c r="C37">
-        <v>10788</v>
+        <v>56</v>
       </c>
       <c r="D37">
-        <v>1160000</v>
+        <v>20000</v>
       </c>
       <c r="E37">
-        <v>930</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>41130</v>
+        <v>41110</v>
       </c>
       <c r="B38" t="str">
-        <v>성남시</v>
+        <v>수원시</v>
       </c>
       <c r="C38">
-        <v>7112</v>
+        <v>10788</v>
       </c>
       <c r="D38">
-        <v>900000</v>
+        <v>1160000</v>
       </c>
       <c r="E38">
-        <v>790</v>
+        <v>930</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>41150</v>
+        <v>41130</v>
       </c>
       <c r="B39" t="str">
-        <v>의정부시</v>
+        <v>성남시</v>
       </c>
       <c r="C39">
-        <v>4312</v>
+        <v>7112</v>
       </c>
       <c r="D39">
-        <v>440000</v>
+        <v>900000</v>
       </c>
       <c r="E39">
-        <v>980</v>
+        <v>790</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>41170</v>
+        <v>41150</v>
       </c>
       <c r="B40" t="str">
-        <v>안양시</v>
+        <v>의정부시</v>
       </c>
       <c r="C40">
-        <v>5376</v>
+        <v>4312</v>
       </c>
       <c r="D40">
-        <v>640000</v>
+        <v>440000</v>
       </c>
       <c r="E40">
-        <v>840</v>
+        <v>980</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>41190</v>
+        <v>41170</v>
       </c>
       <c r="B41" t="str">
-        <v>부천시</v>
+        <v>안양시</v>
       </c>
       <c r="C41">
-        <v>8484</v>
+        <v>5376</v>
       </c>
       <c r="D41">
-        <v>840000</v>
+        <v>640000</v>
       </c>
       <c r="E41">
-        <v>1010</v>
+        <v>840</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>41210</v>
+        <v>41190</v>
       </c>
       <c r="B42" t="str">
-        <v>광명시</v>
+        <v>부천시</v>
       </c>
       <c r="C42">
-        <v>2848</v>
+        <v>8484</v>
       </c>
       <c r="D42">
-        <v>320000</v>
+        <v>840000</v>
       </c>
       <c r="E42">
-        <v>890</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>41220</v>
+        <v>41210</v>
       </c>
       <c r="B43" t="str">
-        <v>평택시</v>
+        <v>광명시</v>
       </c>
       <c r="C43">
-        <v>4800</v>
+        <v>2848</v>
       </c>
       <c r="D43">
-        <v>500000</v>
+        <v>320000</v>
       </c>
       <c r="E43">
-        <v>960</v>
+        <v>890</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>41250</v>
+        <v>41220</v>
       </c>
       <c r="B44" t="str">
-        <v>동두천시</v>
+        <v>평택시</v>
       </c>
       <c r="C44">
-        <v>1012</v>
+        <v>4800</v>
       </c>
       <c r="D44">
-        <v>93000</v>
+        <v>500000</v>
       </c>
       <c r="E44">
-        <v>1090</v>
+        <v>960</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>41270</v>
+        <v>41250</v>
       </c>
       <c r="B45" t="str">
-        <v>안산시</v>
+        <v>동두천시</v>
       </c>
       <c r="C45">
-        <v>8568</v>
+        <v>1012</v>
       </c>
       <c r="D45">
-        <v>720000</v>
+        <v>93000</v>
       </c>
       <c r="E45">
-        <v>1190</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>41280</v>
+        <v>41270</v>
       </c>
       <c r="B46" t="str">
-        <v>고양시</v>
+        <v>안산시</v>
       </c>
       <c r="C46">
-        <v>7770</v>
+        <v>8568</v>
       </c>
       <c r="D46">
-        <v>1050000</v>
+        <v>720000</v>
       </c>
       <c r="E46">
-        <v>740</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>41290</v>
+        <v>41280</v>
       </c>
       <c r="B47" t="str">
-        <v>과천시</v>
+        <v>고양시</v>
       </c>
       <c r="C47">
-        <v>356</v>
+        <v>7770</v>
       </c>
       <c r="D47">
-        <v>66000</v>
+        <v>1050000</v>
       </c>
       <c r="E47">
-        <v>540</v>
+        <v>740</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>41310</v>
+        <v>41290</v>
       </c>
       <c r="B48" t="str">
-        <v>구리시</v>
+        <v>과천시</v>
       </c>
       <c r="C48">
-        <v>1596</v>
+        <v>356</v>
       </c>
       <c r="D48">
-        <v>190000</v>
+        <v>66000</v>
       </c>
       <c r="E48">
-        <v>840</v>
+        <v>540</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>41360</v>
+        <v>41310</v>
       </c>
       <c r="B49" t="str">
-        <v>남양주시</v>
+        <v>구리시</v>
       </c>
       <c r="C49">
-        <v>4624</v>
+        <v>1596</v>
       </c>
       <c r="D49">
-        <v>680000</v>
+        <v>190000</v>
       </c>
       <c r="E49">
-        <v>680</v>
+        <v>840</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>41370</v>
+        <v>41360</v>
       </c>
       <c r="B50" t="str">
-        <v>오산시</v>
+        <v>남양주시</v>
       </c>
       <c r="C50">
-        <v>1738</v>
+        <v>4624</v>
       </c>
       <c r="D50">
-        <v>220000</v>
+        <v>680000</v>
       </c>
       <c r="E50">
-        <v>790</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>41390</v>
+        <v>41370</v>
       </c>
       <c r="B51" t="str">
-        <v>시흥시</v>
+        <v>오산시</v>
       </c>
       <c r="C51">
-        <v>4048</v>
+        <v>1738</v>
       </c>
       <c r="D51">
-        <v>460000</v>
+        <v>220000</v>
       </c>
       <c r="E51">
-        <v>880</v>
+        <v>790</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>41410</v>
+        <v>41390</v>
       </c>
       <c r="B52" t="str">
-        <v>군포시</v>
+        <v>시흥시</v>
       </c>
       <c r="C52">
-        <v>2072</v>
+        <v>4048</v>
       </c>
       <c r="D52">
-        <v>280000</v>
+        <v>460000</v>
       </c>
       <c r="E52">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>41430</v>
+        <v>41410</v>
       </c>
       <c r="B53" t="str">
-        <v>의왕시</v>
+        <v>군포시</v>
       </c>
       <c r="C53">
-        <v>1173</v>
+        <v>2072</v>
       </c>
       <c r="D53">
-        <v>170000</v>
+        <v>280000</v>
       </c>
       <c r="E53">
-        <v>690</v>
+        <v>740</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>41450</v>
+        <v>41430</v>
       </c>
       <c r="B54" t="str">
-        <v>하남시</v>
+        <v>의왕시</v>
       </c>
       <c r="C54">
-        <v>1932</v>
+        <v>1173</v>
       </c>
       <c r="D54">
-        <v>280000</v>
+        <v>170000</v>
       </c>
       <c r="E54">
         <v>690</v>
@@ -1319,16 +1319,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>41460</v>
+        <v>41450</v>
       </c>
       <c r="B55" t="str">
-        <v>용인시</v>
+        <v>하남시</v>
       </c>
       <c r="C55">
-        <v>7452</v>
+        <v>1932</v>
       </c>
       <c r="D55">
-        <v>1080000</v>
+        <v>280000</v>
       </c>
       <c r="E55">
         <v>690</v>
@@ -1336,84 +1336,84 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>41480</v>
+        <v>41460</v>
       </c>
       <c r="B56" t="str">
-        <v>파주시</v>
+        <v>용인시</v>
       </c>
       <c r="C56">
-        <v>3712</v>
+        <v>7452</v>
       </c>
       <c r="D56">
-        <v>470000</v>
+        <v>1080000</v>
       </c>
       <c r="E56">
-        <v>790</v>
+        <v>690</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>41500</v>
+        <v>41480</v>
       </c>
       <c r="B57" t="str">
-        <v>이천시</v>
+        <v>파주시</v>
       </c>
       <c r="C57">
-        <v>1848</v>
+        <v>3712</v>
       </c>
       <c r="D57">
-        <v>220000</v>
+        <v>470000</v>
       </c>
       <c r="E57">
-        <v>840</v>
+        <v>790</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>41550</v>
+        <v>41500</v>
       </c>
       <c r="B58" t="str">
-        <v>안성시</v>
+        <v>이천시</v>
       </c>
       <c r="C58">
-        <v>1692</v>
+        <v>1848</v>
       </c>
       <c r="D58">
-        <v>190000</v>
+        <v>220000</v>
       </c>
       <c r="E58">
-        <v>890</v>
+        <v>840</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>41570</v>
+        <v>41550</v>
       </c>
       <c r="B59" t="str">
-        <v>김포시</v>
+        <v>안성시</v>
       </c>
       <c r="C59">
-        <v>3330</v>
+        <v>1692</v>
       </c>
       <c r="D59">
-        <v>450000</v>
+        <v>190000</v>
       </c>
       <c r="E59">
-        <v>740</v>
+        <v>890</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>41590</v>
+        <v>41570</v>
       </c>
       <c r="B60" t="str">
-        <v>화성시</v>
+        <v>김포시</v>
       </c>
       <c r="C60">
-        <v>6000</v>
+        <v>3330</v>
       </c>
       <c r="D60">
-        <v>810000</v>
+        <v>450000</v>
       </c>
       <c r="E60">
         <v>740</v>
@@ -1421,126 +1421,143 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>41610</v>
+        <v>41590</v>
       </c>
       <c r="B61" t="str">
-        <v>광주시</v>
+        <v>화성시</v>
       </c>
       <c r="C61">
-        <v>2560</v>
+        <v>6000</v>
       </c>
       <c r="D61">
-        <v>330000</v>
+        <v>810000</v>
       </c>
       <c r="E61">
-        <v>790</v>
+        <v>740</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>41630</v>
+        <v>41610</v>
       </c>
       <c r="B62" t="str">
-        <v>양주시</v>
+        <v>광주시</v>
       </c>
       <c r="C62">
-        <v>2052</v>
+        <v>2560</v>
       </c>
       <c r="D62">
-        <v>230000</v>
+        <v>330000</v>
       </c>
       <c r="E62">
-        <v>890</v>
+        <v>790</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>41650</v>
+        <v>41630</v>
       </c>
       <c r="B63" t="str">
-        <v>포천시</v>
+        <v>양주시</v>
       </c>
       <c r="C63">
-        <v>1584</v>
+        <v>2052</v>
       </c>
       <c r="D63">
-        <v>160000</v>
+        <v>230000</v>
       </c>
       <c r="E63">
-        <v>990</v>
+        <v>890</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>41670</v>
+        <v>41650</v>
       </c>
       <c r="B64" t="str">
-        <v>여주시</v>
+        <v>포천시</v>
       </c>
       <c r="C64">
-        <v>924</v>
+        <v>1584</v>
       </c>
       <c r="D64">
-        <v>105000</v>
+        <v>160000</v>
       </c>
       <c r="E64">
-        <v>880</v>
+        <v>990</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>41800</v>
+        <v>41670</v>
       </c>
       <c r="B65" t="str">
-        <v>연천군</v>
+        <v>여주시</v>
       </c>
       <c r="C65">
-        <v>448</v>
+        <v>924</v>
       </c>
       <c r="D65">
-        <v>65000</v>
+        <v>105000</v>
       </c>
       <c r="E65">
-        <v>690</v>
+        <v>880</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>41820</v>
+        <v>41800</v>
       </c>
       <c r="B66" t="str">
-        <v>가평군</v>
+        <v>연천군</v>
       </c>
       <c r="C66">
-        <v>360</v>
+        <v>448</v>
       </c>
       <c r="D66">
-        <v>61000</v>
+        <v>65000</v>
       </c>
       <c r="E66">
-        <v>590</v>
+        <v>690</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
+        <v>41820</v>
+      </c>
+      <c r="B67" t="str">
+        <v>가평군</v>
+      </c>
+      <c r="C67">
+        <v>360</v>
+      </c>
+      <c r="D67">
+        <v>61000</v>
+      </c>
+      <c r="E67">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
         <v>41830</v>
       </c>
-      <c r="B67" t="str">
+      <c r="B68" t="str">
         <v>양평군</v>
       </c>
-      <c r="C67">
+      <c r="C68">
         <v>594</v>
       </c>
-      <c r="D67">
+      <c r="D68">
         <v>108000</v>
       </c>
-      <c r="E67">
+      <c r="E68">
         <v>540</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E68"/>
   </ignoredErrors>
 </worksheet>
 </file>